--- a/tenders/analysis/2026-kfar-bara-17/מודל_כלכלי_מכרז_17-2026_כפר_ברא.xlsx
+++ b/tenders/analysis/2026-kfar-bara-17/מודל_כלכלי_מכרז_17-2026_כפר_ברא.xlsx
@@ -48,7 +48,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">6, 39).</t>
+          <t xml:space="preserve">6, 40).</t>
         </r>
       </text>
     </comment>
@@ -68,7 +68,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">6, 39).</t>
+          <t xml:space="preserve">6, 40).</t>
         </r>
       </text>
     </comment>
@@ -88,7 +88,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">6, 39).</t>
+          <t xml:space="preserve">6, 40).</t>
         </r>
       </text>
     </comment>
@@ -108,7 +108,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">6, 39).</t>
+          <t xml:space="preserve">6, 40).</t>
         </r>
       </text>
     </comment>
@@ -128,7 +128,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">6, 39).</t>
+          <t xml:space="preserve">6, 40).</t>
         </r>
       </text>
     </comment>

--- a/tenders/analysis/2026-kfar-bara-17/מודל_כלכלי_מכרז_17-2026_כפר_ברא.xlsx
+++ b/tenders/analysis/2026-kfar-bara-17/מודל_כלכלי_מכרז_17-2026_כפר_ברא.xlsx
@@ -1026,7 +1026,7 @@
     <t xml:space="preserve">תנאי סף: 5 שנות IT מנוהל ל-2 רשויות, ISO 9001 + 27001, תמיכה 24/7</t>
   </si>
   <si>
-    <t xml:space="preserve">אם לא – רק דרך שותף/קבלן משנה (שאלת הבהרה 11).</t>
+    <t xml:space="preserve">ISO 27001 קיים עד 2028; ISO 9001 – לבדוק. ניסיון IT מנוהל – אם לא, רק דרך שותף/קבלן משנה (שאלת הבהרה 11).</t>
   </si>
   <si>
     <t xml:space="preserve">רווחיות (גיליון תזרים)</t>

--- a/tenders/analysis/2026-kfar-bara-17/מודל_כלכלי_מכרז_17-2026_כפר_ברא.xlsx
+++ b/tenders/analysis/2026-kfar-bara-17/מודל_כלכלי_מכרז_17-2026_כפר_ברא.xlsx
@@ -1026,7 +1026,7 @@
     <t xml:space="preserve">תנאי סף: 5 שנות IT מנוהל ל-2 רשויות, ISO 9001 + 27001, תמיכה 24/7</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 27001 קיים עד 2028; ISO 9001 – לבדוק. ניסיון IT מנוהל – אם לא, רק דרך שותף/קבלן משנה (שאלת הבהרה 11).</t>
+    <t xml:space="preserve">ISO 27001 קיים עד 2028. ISO 9001 – אין (בטיפול, נכון ל-14.10.2026): לא עומדים בתנאי הסף, אלא אם תשובת ההבהרה (שאלות 11, 13) תאפשר חלופה. לעדכן ל-3 ומעלה רק אחרי תשובה חיובית.</t>
   </si>
   <si>
     <t xml:space="preserve">רווחיות (גיליון תזרים)</t>
@@ -7624,11 +7624,11 @@
         <v>0.2</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="35" t="n">
         <f aca="false">B4*C4</f>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>220</v>
@@ -7752,11 +7752,11 @@
       </c>
       <c r="D12" s="36" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="E12" s="13" t="str">
         <f aca="false">IF(C4&lt;3,"לא להגיש – תנאי סף",IF(D12&gt;=3.5,"להגיש",IF(D12&gt;=2.75,"להגיש בתנאים – לפי תשובות ההבהרה","לא להגיש")))</f>
-        <v>להגיש בתנאים – לפי תשובות ההבהרה</v>
+        <v>לא להגיש – תנאי סף</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
